--- a/data/trans_orig/P16A15-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29906</t>
+          <t>29311</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55143</t>
+          <t>54036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45941</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74223</t>
+          <t>72627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80898</t>
+          <t>81217</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118942</t>
+          <t>118564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>637851</t>
+          <t>638958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>663088</t>
+          <t>663683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>614128</t>
+          <t>615724</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>642410</t>
+          <t>644370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262403</t>
+          <t>1262781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1300447</t>
+          <t>1300128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43375</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72322</t>
+          <t>72518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71072</t>
+          <t>71671</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107987</t>
+          <t>107678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121616</t>
+          <t>120728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>170108</t>
+          <t>167439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>889478</t>
+          <t>889282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>918425</t>
+          <t>918757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>860406</t>
+          <t>860715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>897321</t>
+          <t>896722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1760085</t>
+          <t>1762754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1808577</t>
+          <t>1809465</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49679</t>
+          <t>50249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38628</t>
+          <t>39356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65231</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71950</t>
+          <t>71083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106580</t>
+          <t>106766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628830</t>
+          <t>628260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651643</t>
+          <t>651662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>618610</t>
+          <t>617759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645213</t>
+          <t>644485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1255770</t>
+          <t>1255584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1290400</t>
+          <t>1291267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>44129</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69603</t>
+          <t>71954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55553</t>
+          <t>56264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88329</t>
+          <t>89563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106526</t>
+          <t>107448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149513</t>
+          <t>149838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>872619</t>
+          <t>870268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>897036</t>
+          <t>898093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>950283</t>
+          <t>949049</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>983059</t>
+          <t>982348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1831321</t>
+          <t>1830996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1874308</t>
+          <t>1873386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>164412</t>
+          <t>164340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217366</t>
+          <t>218178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238111</t>
+          <t>235995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297241</t>
+          <t>297745</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>413344</t>
+          <t>420869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>500464</t>
+          <t>502330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3058159</t>
+          <t>3057347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3111113</t>
+          <t>3111185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3081956</t>
+          <t>3081452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3141086</t>
+          <t>3143202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6154258</t>
+          <t>6152392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6241378</t>
+          <t>6233853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66983</t>
+          <t>68418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103732</t>
+          <t>103494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78253</t>
+          <t>79059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115691</t>
+          <t>114348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155768</t>
+          <t>157139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210675</t>
+          <t>208226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597034</t>
+          <t>597272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>633783</t>
+          <t>632348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>578647</t>
+          <t>579990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>616085</t>
+          <t>615279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1184429</t>
+          <t>1186878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1239336</t>
+          <t>1237965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85533</t>
+          <t>82654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126360</t>
+          <t>122715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100368</t>
+          <t>99670</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141828</t>
+          <t>141358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193025</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>251965</t>
+          <t>250064</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>891587</t>
+          <t>895232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>932414</t>
+          <t>935293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>884867</t>
+          <t>885337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>926327</t>
+          <t>927025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1792677</t>
+          <t>1794578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1851617</t>
+          <t>1852858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54631</t>
+          <t>53036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87745</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80311</t>
+          <t>80475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119869</t>
+          <t>118619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145073</t>
+          <t>144847</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196950</t>
+          <t>196667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668793</t>
+          <t>669094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>701907</t>
+          <t>703502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656414</t>
+          <t>657664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>695972</t>
+          <t>695808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1335871</t>
+          <t>1336154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1387748</t>
+          <t>1387974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78373</t>
+          <t>76174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119358</t>
+          <t>117381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101618</t>
+          <t>101537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142552</t>
+          <t>143561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193787</t>
+          <t>188699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250744</t>
+          <t>248008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>826572</t>
+          <t>828549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>867557</t>
+          <t>869756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>906211</t>
+          <t>905202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>947145</t>
+          <t>947226</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1743950</t>
+          <t>1746686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1800907</t>
+          <t>1805995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>311936</t>
+          <t>315960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>386535</t>
+          <t>387073</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,82 +4067,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>435567</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>397571</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>482700</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>787555</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>731552</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>845405</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>11,3%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>435567</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>395711</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>474950</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>787555</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>734156</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>840868</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3034646</t>
+          <t>3034108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3109245</t>
+          <t>3105221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,82 +4180,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>88,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3110513</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3063380</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3148509</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>87,72%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>86,39%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6179706</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6121856</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6235709</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>88,7%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3110513</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3071130</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3150369</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>86,61%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>88,84%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>5774</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6179706</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6126393</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6233105</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64317</t>
+          <t>63407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95546</t>
+          <t>98425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75463</t>
+          <t>73559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111066</t>
+          <t>110567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148839</t>
+          <t>147248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195974</t>
+          <t>195741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>579254</t>
+          <t>576375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>610483</t>
+          <t>611393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>561773</t>
+          <t>562272</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>597376</t>
+          <t>599280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1151665</t>
+          <t>1151898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1198800</t>
+          <t>1200391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80341</t>
+          <t>79345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119578</t>
+          <t>119161</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104634</t>
+          <t>104809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148456</t>
+          <t>150120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194737</t>
+          <t>194530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>253733</t>
+          <t>257100</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>902853</t>
+          <t>903270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>942090</t>
+          <t>943086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>894457</t>
+          <t>892793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>938279</t>
+          <t>938104</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1811611</t>
+          <t>1808244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1870607</t>
+          <t>1870814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>56893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91740</t>
+          <t>89350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46637</t>
+          <t>46007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81339</t>
+          <t>79136</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111168</t>
+          <t>114429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158896</t>
+          <t>156183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667812</t>
+          <t>670202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>701977</t>
+          <t>702659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>703672</t>
+          <t>705875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>738374</t>
+          <t>739004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1385667</t>
+          <t>1388380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1433395</t>
+          <t>1430134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56003</t>
+          <t>55639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87079</t>
+          <t>87750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93995</t>
+          <t>92424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132924</t>
+          <t>136335</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156692</t>
+          <t>156000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208851</t>
+          <t>212186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>850488</t>
+          <t>849817</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>881564</t>
+          <t>881928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>910855</t>
+          <t>907444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>949784</t>
+          <t>951355</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1772495</t>
+          <t>1769160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1824654</t>
+          <t>1825346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>283875</t>
+          <t>288562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>351976</t>
+          <t>356536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>351406</t>
+          <t>348835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>430726</t>
+          <t>426247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>655378</t>
+          <t>655952</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>761595</t>
+          <t>761295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3042374</t>
+          <t>3037814</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3110475</t>
+          <t>3105788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3113816</t>
+          <t>3118295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3193136</t>
+          <t>3195707</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6177297</t>
+          <t>6177597</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6283514</t>
+          <t>6282940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72471</t>
+          <t>73702</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104626</t>
+          <t>104358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93383</t>
+          <t>92554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118569</t>
+          <t>118369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>172055</t>
+          <t>174228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215645</t>
+          <t>215501</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>530815</t>
+          <t>531083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>562970</t>
+          <t>561739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>557183</t>
+          <t>557383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>582369</t>
+          <t>583198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1095549</t>
+          <t>1095693</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1139139</t>
+          <t>1136966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60062</t>
+          <t>52008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144430</t>
+          <t>141963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114355</t>
+          <t>115976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146664</t>
+          <t>147792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>147574</t>
+          <t>153933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>278688</t>
+          <t>278718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1048434</t>
+          <t>1050901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1132802</t>
+          <t>1140856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>811442</t>
+          <t>810314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>843751</t>
+          <t>842130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1872283</t>
+          <t>1872253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2003397</t>
+          <t>1997038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70291</t>
+          <t>70579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104259</t>
+          <t>106265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99413</t>
+          <t>99049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>592006</t>
+          <t>633866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183007</t>
+          <t>183671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>806016</t>
+          <t>872737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>599425</t>
+          <t>597419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633393</t>
+          <t>633105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>340794</t>
+          <t>298934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>833387</t>
+          <t>833751</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>830468</t>
+          <t>763747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1453477</t>
+          <t>1452813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97821</t>
+          <t>98066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134116</t>
+          <t>134176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125912</t>
+          <t>128892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176684</t>
+          <t>177626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>239110</t>
+          <t>231548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>296801</t>
+          <t>296524</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>792715</t>
+          <t>792655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>829010</t>
+          <t>828765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>914690</t>
+          <t>913748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965462</t>
+          <t>962482</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1721404</t>
+          <t>1721681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1779095</t>
+          <t>1786657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>310253</t>
+          <t>294988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>443635</t>
+          <t>442832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>491218</t>
+          <t>486816</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1258568</t>
+          <t>1202240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>874918</t>
+          <t>867714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1732706</t>
+          <t>1724811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3015185</t>
+          <t>3015988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3148567</t>
+          <t>3163832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2399465</t>
+          <t>2455793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3166815</t>
+          <t>3171217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5384147</t>
+          <t>5392042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6241935</t>
+          <t>6249139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A15-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29311</t>
+          <t>29639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54036</t>
+          <t>53935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>43506</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72627</t>
+          <t>71836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81217</t>
+          <t>82104</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118564</t>
+          <t>119896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>638958</t>
+          <t>639059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>663683</t>
+          <t>663355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>615724</t>
+          <t>616515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>644370</t>
+          <t>644845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262781</t>
+          <t>1261449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1300128</t>
+          <t>1299241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>43569</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72518</t>
+          <t>73806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71671</t>
+          <t>70632</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107678</t>
+          <t>106649</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120728</t>
+          <t>121613</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167439</t>
+          <t>168446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>889282</t>
+          <t>887994</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>918757</t>
+          <t>918231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>860715</t>
+          <t>861744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>896722</t>
+          <t>897761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1762754</t>
+          <t>1761747</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1809465</t>
+          <t>1808580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26847</t>
+          <t>26850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50249</t>
+          <t>49719</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>38895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>64362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71083</t>
+          <t>70350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106766</t>
+          <t>107406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628260</t>
+          <t>628790</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651662</t>
+          <t>651659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>617759</t>
+          <t>619479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>644485</t>
+          <t>644946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1255584</t>
+          <t>1254944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291267</t>
+          <t>1292000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44129</t>
+          <t>43433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71954</t>
+          <t>70377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56264</t>
+          <t>55001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89563</t>
+          <t>88900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107448</t>
+          <t>105959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149838</t>
+          <t>148745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>870268</t>
+          <t>871845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>898093</t>
+          <t>898789</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>949049</t>
+          <t>949712</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>982348</t>
+          <t>983611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1830996</t>
+          <t>1832089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1873386</t>
+          <t>1874875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>164340</t>
+          <t>164565</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>218178</t>
+          <t>216536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>235995</t>
+          <t>236389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297745</t>
+          <t>297601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>420869</t>
+          <t>419808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>502330</t>
+          <t>496259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3057347</t>
+          <t>3058989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3111185</t>
+          <t>3110960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3081452</t>
+          <t>3081596</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3143202</t>
+          <t>3142808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6152392</t>
+          <t>6158463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6233853</t>
+          <t>6234914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68418</t>
+          <t>68981</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103494</t>
+          <t>105259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79059</t>
+          <t>78140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114348</t>
+          <t>114515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157139</t>
+          <t>155471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208226</t>
+          <t>206372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597272</t>
+          <t>595507</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632348</t>
+          <t>631785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>579990</t>
+          <t>579823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>615279</t>
+          <t>616198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1186878</t>
+          <t>1188732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1237965</t>
+          <t>1239633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82654</t>
+          <t>84112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122715</t>
+          <t>122826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99670</t>
+          <t>100209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141358</t>
+          <t>142010</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>191784</t>
+          <t>192188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250064</t>
+          <t>251210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>895232</t>
+          <t>895121</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>935293</t>
+          <t>933835</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>885337</t>
+          <t>884685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>927025</t>
+          <t>926486</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1794578</t>
+          <t>1793432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1852858</t>
+          <t>1852454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53036</t>
+          <t>53315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87444</t>
+          <t>88532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80475</t>
+          <t>80226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118619</t>
+          <t>121401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144847</t>
+          <t>142698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196667</t>
+          <t>195563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>669094</t>
+          <t>668006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>703502</t>
+          <t>703223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>657664</t>
+          <t>654882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>695808</t>
+          <t>696057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1336154</t>
+          <t>1337258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1387974</t>
+          <t>1390123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76174</t>
+          <t>79524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117381</t>
+          <t>117287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101537</t>
+          <t>102429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143561</t>
+          <t>146307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>188699</t>
+          <t>191200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248008</t>
+          <t>248553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>828549</t>
+          <t>828643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869756</t>
+          <t>866406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>905202</t>
+          <t>902456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>947226</t>
+          <t>946334</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1746686</t>
+          <t>1746141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1805995</t>
+          <t>1803494</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>315960</t>
+          <t>318298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>387073</t>
+          <t>393069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>397571</t>
+          <t>397636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>482700</t>
+          <t>475543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>731552</t>
+          <t>738161</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>845405</t>
+          <t>841006</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3034108</t>
+          <t>3028112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3105221</t>
+          <t>3102883</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3063380</t>
+          <t>3070537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3148509</t>
+          <t>3148444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6121856</t>
+          <t>6126255</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6235709</t>
+          <t>6229100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63407</t>
+          <t>62893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98425</t>
+          <t>96583</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73559</t>
+          <t>74922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110567</t>
+          <t>111742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147248</t>
+          <t>146619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195741</t>
+          <t>195471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>576375</t>
+          <t>578217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>611393</t>
+          <t>611907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>562272</t>
+          <t>561097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>599280</t>
+          <t>597917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1151898</t>
+          <t>1152168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1200391</t>
+          <t>1201020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79345</t>
+          <t>79702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119161</t>
+          <t>116534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104809</t>
+          <t>104320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150120</t>
+          <t>150184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194530</t>
+          <t>194188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257100</t>
+          <t>252527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>903270</t>
+          <t>905897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>943086</t>
+          <t>942729</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>892793</t>
+          <t>892729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>938104</t>
+          <t>938593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1808244</t>
+          <t>1812817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1870814</t>
+          <t>1871156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>57456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89350</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>47535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79136</t>
+          <t>79025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114429</t>
+          <t>112522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156183</t>
+          <t>159579</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670202</t>
+          <t>669832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>702659</t>
+          <t>702096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>705875</t>
+          <t>705986</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>739004</t>
+          <t>737476</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1388380</t>
+          <t>1384984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1430134</t>
+          <t>1432041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55639</t>
+          <t>55994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87750</t>
+          <t>86526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92424</t>
+          <t>92165</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136335</t>
+          <t>135180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156000</t>
+          <t>156580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212186</t>
+          <t>210809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>849817</t>
+          <t>851041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>881928</t>
+          <t>881573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>907444</t>
+          <t>908599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>951355</t>
+          <t>951614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1769160</t>
+          <t>1770537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1825346</t>
+          <t>1824766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>288562</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>351265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348835</t>
+          <t>355114</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>426247</t>
+          <t>430273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>655952</t>
+          <t>657075</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>761295</t>
+          <t>762250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3037814</t>
+          <t>3043085</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3105788</t>
+          <t>3110609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3118295</t>
+          <t>3114269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3195707</t>
+          <t>3189428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6177597</t>
+          <t>6176642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6282940</t>
+          <t>6281817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87809</t>
+          <t>93466</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73702</t>
+          <t>77733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104358</t>
+          <t>110977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>105465</t>
+          <t>111801</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92554</t>
+          <t>98285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>125549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>193274</t>
+          <t>205267</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174228</t>
+          <t>185049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215501</t>
+          <t>228157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>547632</t>
+          <t>597244</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>531083</t>
+          <t>579733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>561739</t>
+          <t>612977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>570287</t>
+          <t>621312</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>557383</t>
+          <t>607564</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>583198</t>
+          <t>634828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1117920</t>
+          <t>1218556</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1095693</t>
+          <t>1195666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1136966</t>
+          <t>1238774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107629</t>
+          <t>116546</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52008</t>
+          <t>98937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141963</t>
+          <t>137148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>130610</t>
+          <t>143478</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115976</t>
+          <t>126042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147792</t>
+          <t>160715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>238239</t>
+          <t>260024</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153933</t>
+          <t>235866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>278718</t>
+          <t>284902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1085235</t>
+          <t>932371</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1050901</t>
+          <t>911769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1140856</t>
+          <t>949980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>827496</t>
+          <t>927360</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>810314</t>
+          <t>910123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>842130</t>
+          <t>944796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1912732</t>
+          <t>1859731</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1872253</t>
+          <t>1834853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1997038</t>
+          <t>1883889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85896</t>
+          <t>95757</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70579</t>
+          <t>79551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106265</t>
+          <t>115067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>287176</t>
+          <t>93013</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99049</t>
+          <t>78786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>633866</t>
+          <t>108862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>373072</t>
+          <t>188770</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183671</t>
+          <t>166919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>872737</t>
+          <t>214261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>617788</t>
+          <t>706329</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597419</t>
+          <t>687019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633105</t>
+          <t>722535</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>645624</t>
+          <t>718650</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>298934</t>
+          <t>702801</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>833751</t>
+          <t>732877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1263412</t>
+          <t>1424978</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>763747</t>
+          <t>1399487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1452813</t>
+          <t>1446829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636484</t>
+          <t>1613748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>114604</t>
+          <t>117725</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>101001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134176</t>
+          <t>136766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>155156</t>
+          <t>170038</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128892</t>
+          <t>151251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177626</t>
+          <t>188706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>269761</t>
+          <t>287764</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231548</t>
+          <t>262714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>296524</t>
+          <t>314716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>812227</t>
+          <t>872337</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>792655</t>
+          <t>853296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>828765</t>
+          <t>889061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>936218</t>
+          <t>946993</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>913748</t>
+          <t>928325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>962482</t>
+          <t>965780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1748444</t>
+          <t>1819329</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1721681</t>
+          <t>1792377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1786657</t>
+          <t>1844379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>395938</t>
+          <t>423495</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>294988</t>
+          <t>390015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>442832</t>
+          <t>458262</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>678408</t>
+          <t>518329</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>486816</t>
+          <t>486233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1202240</t>
+          <t>551151</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1074346</t>
+          <t>941824</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>867714</t>
+          <t>891729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1724811</t>
+          <t>993896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3062882</t>
+          <t>3108280</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3015988</t>
+          <t>3073513</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3163832</t>
+          <t>3141760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2979625</t>
+          <t>3214316</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2455793</t>
+          <t>3181494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3171217</t>
+          <t>3246412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6042507</t>
+          <t>6322595</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5392042</t>
+          <t>6270523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6249139</t>
+          <t>6372690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
